--- a/LFCS_matriz.xlsx
+++ b/LFCS_matriz.xlsx
@@ -236,7 +236,7 @@
     <t xml:space="preserve">Inspeccionar y gestionar pools y volúmenes con virsh.</t>
   </si>
   <si>
-    <t xml:space="preserve">Contenedores Docker y Podman</t>
+    <t xml:space="preserve">Contenedores Docker-Podman</t>
   </si>
   <si>
     <t xml:space="preserve">Imágenes y contenedores</t>
@@ -1361,7 +1361,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1408,10 +1408,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2205,7 +2201,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="13.58"/>
@@ -2255,7 +2251,7 @@
       <c r="F2" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -2276,7 +2272,7 @@
       <c r="F3" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -2297,7 +2293,7 @@
       <c r="F4" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
@@ -2318,7 +2314,7 @@
       <c r="F5" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
@@ -2339,7 +2335,7 @@
       <c r="F6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
@@ -2348,7 +2344,7 @@
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -2357,10 +2353,10 @@
       <c r="E7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
@@ -2369,7 +2365,7 @@
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -2378,10 +2374,10 @@
       <c r="E8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="12"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
@@ -2390,7 +2386,7 @@
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -2399,10 +2395,10 @@
       <c r="E9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="12"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -2411,7 +2407,7 @@
       <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -2420,10 +2416,10 @@
       <c r="E10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
@@ -2432,7 +2428,7 @@
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -2441,10 +2437,10 @@
       <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
@@ -2453,7 +2449,7 @@
       <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -2462,10 +2458,10 @@
       <c r="E12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" s="12"/>
+      <c r="F12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
@@ -2474,7 +2470,7 @@
       <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="9" t="s">
@@ -2483,10 +2479,10 @@
       <c r="E13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="12"/>
+      <c r="F13" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
@@ -2495,7 +2491,7 @@
       <c r="B14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -2504,10 +2500,10 @@
       <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="12"/>
+      <c r="F14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
@@ -2516,7 +2512,7 @@
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
@@ -2525,10 +2521,10 @@
       <c r="E15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" s="12"/>
+      <c r="F15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
@@ -2537,7 +2533,7 @@
       <c r="B16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="9" t="s">
@@ -2546,10 +2542,10 @@
       <c r="E16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="12"/>
+      <c r="F16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
@@ -2558,7 +2554,7 @@
       <c r="B17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="9" t="s">
@@ -2567,19 +2563,19 @@
       <c r="E17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="9" t="s">
@@ -2588,19 +2584,19 @@
       <c r="E18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="12"/>
+      <c r="F18" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D19" s="9" t="s">
@@ -2609,19 +2605,19 @@
       <c r="E19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="12"/>
+      <c r="F19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="9" t="s">
@@ -2630,19 +2626,19 @@
       <c r="E20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="12"/>
+      <c r="F20" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -2651,19 +2647,19 @@
       <c r="E21" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="12"/>
+      <c r="F21" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="21" t="s">
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -2672,19 +2668,19 @@
       <c r="E22" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="12"/>
+      <c r="F22" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="21" t="s">
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D23" s="9" t="s">
@@ -2693,19 +2689,19 @@
       <c r="E23" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" s="12"/>
+      <c r="F23" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="21" t="s">
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="9" t="s">
@@ -2714,19 +2710,19 @@
       <c r="E24" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" s="12"/>
+      <c r="F24" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="23" t="s">
+      <c r="B25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>61</v>
       </c>
       <c r="D25" s="9" t="s">
@@ -2735,19 +2731,19 @@
       <c r="E25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="23" t="s">
+      <c r="B26" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="9" t="s">
@@ -2756,19 +2752,19 @@
       <c r="E26" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="23" t="s">
+      <c r="B27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>61</v>
       </c>
       <c r="D27" s="9" t="s">
@@ -2777,19 +2773,19 @@
       <c r="E27" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="12"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="23" t="s">
+      <c r="B28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>61</v>
       </c>
       <c r="D28" s="9" t="s">
@@ -2798,19 +2794,19 @@
       <c r="E28" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="12"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="25" t="s">
+      <c r="B29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>70</v>
       </c>
       <c r="D29" s="9" t="s">
@@ -2819,19 +2815,19 @@
       <c r="E29" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="G29" s="12"/>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="25" t="s">
+      <c r="B30" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="9" t="s">
@@ -2840,19 +2836,19 @@
       <c r="E30" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" s="12"/>
+      <c r="F30" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>70</v>
       </c>
       <c r="D31" s="9" t="s">
@@ -2861,19 +2857,19 @@
       <c r="E31" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="12"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="25" t="s">
+      <c r="B32" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="24" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="9" t="s">
@@ -2882,19 +2878,19 @@
       <c r="E32" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="12"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="27" t="s">
+      <c r="B33" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D33" s="9" t="s">
@@ -2903,19 +2899,19 @@
       <c r="E33" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="12"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="27" t="s">
+      <c r="B34" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D34" s="9" t="s">
@@ -2924,19 +2920,19 @@
       <c r="E34" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G34" s="12"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="27" t="s">
+      <c r="B35" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D35" s="9" t="s">
@@ -2945,19 +2941,19 @@
       <c r="E35" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="28" t="n">
+      <c r="F35" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="12"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="27" t="s">
+      <c r="B36" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D36" s="9" t="s">
@@ -2966,19 +2962,19 @@
       <c r="E36" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="12"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="27" t="s">
+      <c r="B37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D37" s="9" t="s">
@@ -2987,19 +2983,19 @@
       <c r="E37" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F37" s="28" t="n">
+      <c r="F37" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="12"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="27" t="s">
+      <c r="B38" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D38" s="9" t="s">
@@ -3008,19 +3004,19 @@
       <c r="E38" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="12"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="29" t="s">
+      <c r="B39" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D39" s="9" t="s">
@@ -3029,19 +3025,19 @@
       <c r="E39" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="30" t="n">
+      <c r="F39" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="12"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="29" t="s">
+      <c r="B40" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D40" s="9" t="s">
@@ -3050,19 +3046,19 @@
       <c r="E40" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F40" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" s="12"/>
+      <c r="F40" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="29" t="s">
+      <c r="B41" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D41" s="9" t="s">
@@ -3071,19 +3067,19 @@
       <c r="E41" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="F41" s="30" t="n">
+      <c r="F41" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="G41" s="12"/>
+      <c r="G41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="29" t="s">
+      <c r="B42" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D42" s="9" t="s">
@@ -3092,19 +3088,19 @@
       <c r="E42" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F42" s="30" t="n">
+      <c r="F42" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="12"/>
+      <c r="G42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="29" t="s">
+      <c r="B43" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D43" s="9" t="s">
@@ -3113,19 +3109,19 @@
       <c r="E43" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="30" t="n">
+      <c r="F43" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="G43" s="12"/>
+      <c r="G43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="29" t="s">
+      <c r="B44" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D44" s="9" t="s">
@@ -3134,19 +3130,19 @@
       <c r="E44" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F44" s="30" t="n">
+      <c r="F44" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="12"/>
+      <c r="G44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="29" t="s">
+      <c r="B45" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="28" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="9" t="s">
@@ -3155,19 +3151,19 @@
       <c r="E45" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" s="12"/>
+      <c r="F45" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="31" t="s">
+      <c r="B46" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="30" t="s">
         <v>108</v>
       </c>
       <c r="D46" s="9" t="s">
@@ -3176,19 +3172,19 @@
       <c r="E46" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F46" s="32" t="n">
+      <c r="F46" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G46" s="12"/>
+      <c r="G46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="31" t="s">
+      <c r="B47" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="30" t="s">
         <v>108</v>
       </c>
       <c r="D47" s="9" t="s">
@@ -3197,19 +3193,19 @@
       <c r="E47" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F47" s="32" t="n">
+      <c r="F47" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="12"/>
+      <c r="G47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="31" t="s">
+      <c r="B48" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="30" t="s">
         <v>108</v>
       </c>
       <c r="D48" s="9" t="s">
@@ -3218,19 +3214,19 @@
       <c r="E48" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F48" s="32" t="n">
+      <c r="F48" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="12"/>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="33" t="s">
+      <c r="B49" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="32" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="9" t="s">
@@ -3239,19 +3235,19 @@
       <c r="E49" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F49" s="34" t="n">
+      <c r="F49" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="G49" s="12"/>
+      <c r="G49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="33" t="s">
+      <c r="B50" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="32" t="s">
         <v>115</v>
       </c>
       <c r="D50" s="9" t="s">
@@ -3260,19 +3256,19 @@
       <c r="E50" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F50" s="34" t="n">
+      <c r="F50" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="G50" s="12"/>
+      <c r="G50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="35" t="s">
+      <c r="B51" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="34" t="s">
         <v>120</v>
       </c>
       <c r="D51" s="9" t="s">
@@ -3281,19 +3277,19 @@
       <c r="E51" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F51" s="36" t="n">
+      <c r="F51" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="G51" s="12"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="35" t="s">
+      <c r="B52" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="34" t="s">
         <v>120</v>
       </c>
       <c r="D52" s="9" t="s">
@@ -3302,19 +3298,19 @@
       <c r="E52" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F52" s="36" t="n">
+      <c r="F52" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="G52" s="12"/>
+      <c r="G52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="35" t="s">
+      <c r="B53" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="34" t="s">
         <v>120</v>
       </c>
       <c r="D53" s="9" t="s">
@@ -3323,19 +3319,19 @@
       <c r="E53" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F53" s="36" t="n">
+      <c r="F53" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="G53" s="12"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="37" t="s">
+      <c r="B54" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="36" t="s">
         <v>127</v>
       </c>
       <c r="D54" s="9" t="s">
@@ -3344,19 +3340,19 @@
       <c r="E54" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F54" s="38" t="n">
+      <c r="F54" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="G54" s="12"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="37" t="s">
+      <c r="B55" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="36" t="s">
         <v>127</v>
       </c>
       <c r="D55" s="9" t="s">
@@ -3365,19 +3361,19 @@
       <c r="E55" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F55" s="38" t="n">
+      <c r="F55" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="12"/>
+      <c r="G55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="37" t="s">
+      <c r="B56" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="36" t="s">
         <v>127</v>
       </c>
       <c r="D56" s="9" t="s">
@@ -3386,19 +3382,19 @@
       <c r="E56" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F56" s="38" t="n">
+      <c r="F56" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="G56" s="12"/>
+      <c r="G56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="37" t="s">
+      <c r="B57" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="36" t="s">
         <v>127</v>
       </c>
       <c r="D57" s="9" t="s">
@@ -3407,19 +3403,19 @@
       <c r="E57" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F57" s="38" t="n">
+      <c r="F57" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="G57" s="12"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="37" t="s">
+      <c r="B58" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="36" t="s">
         <v>127</v>
       </c>
       <c r="D58" s="9" t="s">
@@ -3428,19 +3424,19 @@
       <c r="E58" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="F58" s="38" t="n">
+      <c r="F58" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="12"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="39" t="s">
+      <c r="B59" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D59" s="9" t="s">
@@ -3449,19 +3445,19 @@
       <c r="E59" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="40" t="n">
+      <c r="F59" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="G59" s="12"/>
+      <c r="G59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B60" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="39" t="s">
+      <c r="B60" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D60" s="9" t="s">
@@ -3470,19 +3466,19 @@
       <c r="E60" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F60" s="40" t="n">
+      <c r="F60" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="G60" s="12"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="39" t="s">
+      <c r="B61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="9" t="s">
@@ -3491,19 +3487,19 @@
       <c r="E61" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F61" s="40" t="n">
+      <c r="F61" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="G61" s="12"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="39" t="s">
+      <c r="B62" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D62" s="9" t="s">
@@ -3512,19 +3508,19 @@
       <c r="E62" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F62" s="40" t="n">
+      <c r="F62" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="G62" s="12"/>
+      <c r="G62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="39" t="s">
+      <c r="B63" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="38" t="s">
         <v>138</v>
       </c>
       <c r="D63" s="9" t="s">
@@ -3533,19 +3529,19 @@
       <c r="E63" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F63" s="40" t="n">
+      <c r="F63" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G63" s="12"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="41" t="s">
+      <c r="B64" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="40" t="s">
         <v>149</v>
       </c>
       <c r="D64" s="9" t="s">
@@ -3554,19 +3550,19 @@
       <c r="E64" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F64" s="42" t="n">
+      <c r="F64" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="G64" s="12"/>
+      <c r="G64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B65" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="41" t="s">
+      <c r="B65" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="40" t="s">
         <v>149</v>
       </c>
       <c r="D65" s="9" t="s">
@@ -3575,19 +3571,19 @@
       <c r="E65" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F65" s="42" t="n">
+      <c r="F65" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="G65" s="12"/>
+      <c r="G65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="41" t="s">
+      <c r="B66" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="40" t="s">
         <v>149</v>
       </c>
       <c r="D66" s="9" t="s">
@@ -3596,19 +3592,19 @@
       <c r="E66" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="F66" s="42" t="n">
+      <c r="F66" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="G66" s="12"/>
+      <c r="G66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="43" t="s">
+      <c r="B67" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="42" t="s">
         <v>156</v>
       </c>
       <c r="D67" s="9" t="s">
@@ -3617,19 +3613,19 @@
       <c r="E67" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F67" s="44" t="n">
+      <c r="F67" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="G67" s="12"/>
+      <c r="G67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="43" t="s">
+      <c r="B68" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="42" t="s">
         <v>156</v>
       </c>
       <c r="D68" s="9" t="s">
@@ -3638,19 +3634,19 @@
       <c r="E68" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="44" t="n">
+      <c r="F68" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="G68" s="12"/>
+      <c r="G68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="43" t="s">
+      <c r="B69" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="42" t="s">
         <v>156</v>
       </c>
       <c r="D69" s="9" t="s">
@@ -3659,19 +3655,19 @@
       <c r="E69" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F69" s="44" t="n">
+      <c r="F69" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="G69" s="12"/>
+      <c r="G69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C70" s="45" t="s">
+      <c r="C70" s="44" t="s">
         <v>165</v>
       </c>
       <c r="D70" s="9" t="s">
@@ -3680,19 +3676,19 @@
       <c r="E70" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="F70" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G70" s="12"/>
+      <c r="F70" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C71" s="45" t="s">
+      <c r="C71" s="44" t="s">
         <v>165</v>
       </c>
       <c r="D71" s="9" t="s">
@@ -3701,19 +3697,19 @@
       <c r="E71" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F71" s="46" t="n">
+      <c r="F71" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="G71" s="12"/>
+      <c r="G71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C72" s="45" t="s">
+      <c r="C72" s="44" t="s">
         <v>165</v>
       </c>
       <c r="D72" s="9" t="s">
@@ -3722,19 +3718,19 @@
       <c r="E72" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F72" s="46" t="n">
+      <c r="F72" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="G72" s="12"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="45" t="s">
+      <c r="C73" s="44" t="s">
         <v>165</v>
       </c>
       <c r="D73" s="9" t="s">
@@ -3743,19 +3739,19 @@
       <c r="E73" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F73" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G73" s="12"/>
+      <c r="F73" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C74" s="45" t="s">
+      <c r="C74" s="44" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="9" t="s">
@@ -3764,19 +3760,19 @@
       <c r="E74" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F74" s="46" t="n">
+      <c r="F74" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="G74" s="12"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
+      <c r="A75" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D75" s="9" t="s">
@@ -3785,19 +3781,19 @@
       <c r="E75" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="G75" s="12"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D76" s="9" t="s">
@@ -3806,19 +3802,19 @@
       <c r="E76" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="G76" s="12"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D77" s="9" t="s">
@@ -3827,19 +3823,19 @@
       <c r="E77" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="F77" s="16" t="n">
+      <c r="F77" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G77" s="12"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D78" s="9" t="s">
@@ -3848,19 +3844,19 @@
       <c r="E78" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F78" s="16" t="n">
+      <c r="F78" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="G78" s="12"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D79" s="9" t="s">
@@ -3869,19 +3865,19 @@
       <c r="E79" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F79" s="16" t="n">
+      <c r="F79" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="G79" s="12"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D80" s="9" t="s">
@@ -3890,19 +3886,19 @@
       <c r="E80" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F80" s="16" t="n">
+      <c r="F80" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="G80" s="12"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C81" s="47" t="s">
+      <c r="C81" s="46" t="s">
         <v>189</v>
       </c>
       <c r="D81" s="9" t="s">
@@ -3911,19 +3907,19 @@
       <c r="E81" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="F81" s="48" t="n">
+      <c r="F81" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G81" s="12"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C82" s="47" t="s">
+      <c r="C82" s="46" t="s">
         <v>189</v>
       </c>
       <c r="D82" s="9" t="s">
@@ -3932,19 +3928,19 @@
       <c r="E82" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F82" s="48" t="n">
+      <c r="F82" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="12"/>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="47" t="s">
+      <c r="C83" s="46" t="s">
         <v>189</v>
       </c>
       <c r="D83" s="9" t="s">
@@ -3953,19 +3949,19 @@
       <c r="E83" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F83" s="48" t="n">
+      <c r="F83" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G83" s="12"/>
+      <c r="G83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="47" t="s">
+      <c r="C84" s="46" t="s">
         <v>189</v>
       </c>
       <c r="D84" s="9" t="s">
@@ -3974,19 +3970,19 @@
       <c r="E84" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F84" s="48" t="n">
+      <c r="F84" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G84" s="12"/>
+      <c r="G84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="16" t="s">
         <v>198</v>
       </c>
       <c r="D85" s="9" t="s">
@@ -3995,19 +3991,19 @@
       <c r="E85" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F85" s="18" t="n">
+      <c r="F85" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G85" s="12"/>
+      <c r="G85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="16" t="s">
         <v>198</v>
       </c>
       <c r="D86" s="9" t="s">
@@ -4016,19 +4012,19 @@
       <c r="E86" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F86" s="18" t="n">
+      <c r="F86" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G86" s="12"/>
+      <c r="G86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="16" t="s">
         <v>198</v>
       </c>
       <c r="D87" s="9" t="s">
@@ -4037,19 +4033,19 @@
       <c r="E87" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F87" s="18" t="n">
+      <c r="F87" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G87" s="12"/>
+      <c r="G87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C88" s="49" t="s">
+      <c r="C88" s="48" t="s">
         <v>205</v>
       </c>
       <c r="D88" s="9" t="s">
@@ -4058,19 +4054,19 @@
       <c r="E88" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F88" s="50" t="n">
+      <c r="F88" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G88" s="12"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C89" s="49" t="s">
+      <c r="C89" s="48" t="s">
         <v>205</v>
       </c>
       <c r="D89" s="9" t="s">
@@ -4079,19 +4075,19 @@
       <c r="E89" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="F89" s="50" t="n">
+      <c r="F89" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G89" s="12"/>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C90" s="49" t="s">
+      <c r="C90" s="48" t="s">
         <v>205</v>
       </c>
       <c r="D90" s="9" t="s">
@@ -4100,19 +4096,19 @@
       <c r="E90" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="F90" s="50" t="n">
+      <c r="F90" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="G90" s="12"/>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C91" s="49" t="s">
+      <c r="C91" s="48" t="s">
         <v>205</v>
       </c>
       <c r="D91" s="9" t="s">
@@ -4121,19 +4117,19 @@
       <c r="E91" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="F91" s="50" t="n">
+      <c r="F91" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G91" s="12"/>
+      <c r="G91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="22" t="s">
         <v>214</v>
       </c>
       <c r="D92" s="9" t="s">
@@ -4142,19 +4138,19 @@
       <c r="E92" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F92" s="24" t="n">
+      <c r="F92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="G92" s="12"/>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="22" t="s">
         <v>214</v>
       </c>
       <c r="D93" s="9" t="s">
@@ -4163,19 +4159,19 @@
       <c r="E93" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="F93" s="24" t="n">
+      <c r="F93" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="12"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="22" t="s">
         <v>214</v>
       </c>
       <c r="D94" s="9" t="s">
@@ -4184,19 +4180,19 @@
       <c r="E94" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="F94" s="24" t="n">
+      <c r="F94" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="G94" s="12"/>
+      <c r="G94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C95" s="51" t="s">
+      <c r="C95" s="50" t="s">
         <v>221</v>
       </c>
       <c r="D95" s="9" t="s">
@@ -4205,19 +4201,19 @@
       <c r="E95" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F95" s="52" t="n">
+      <c r="F95" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="G95" s="12"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C96" s="51" t="s">
+      <c r="C96" s="50" t="s">
         <v>221</v>
       </c>
       <c r="D96" s="9" t="s">
@@ -4226,19 +4222,19 @@
       <c r="E96" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F96" s="52" t="n">
+      <c r="F96" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="G96" s="12"/>
+      <c r="G96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="s">
+      <c r="A97" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C97" s="51" t="s">
+      <c r="C97" s="50" t="s">
         <v>221</v>
       </c>
       <c r="D97" s="9" t="s">
@@ -4247,19 +4243,19 @@
       <c r="E97" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F97" s="52" t="n">
-        <v>8</v>
-      </c>
-      <c r="G97" s="12"/>
+      <c r="F97" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C98" s="53" t="s">
+      <c r="C98" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D98" s="9" t="s">
@@ -4268,19 +4264,19 @@
       <c r="E98" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F98" s="54" t="n">
-        <v>8</v>
-      </c>
-      <c r="G98" s="12"/>
+      <c r="F98" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C99" s="53" t="s">
+      <c r="C99" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D99" s="9" t="s">
@@ -4289,19 +4285,19 @@
       <c r="E99" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="F99" s="54" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" s="12"/>
+      <c r="F99" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="12" t="s">
+      <c r="A100" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C100" s="53" t="s">
+      <c r="C100" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D100" s="9" t="s">
@@ -4310,19 +4306,19 @@
       <c r="E100" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="F100" s="54" t="n">
+      <c r="F100" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G100" s="12"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="12" t="s">
+      <c r="A101" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C101" s="53" t="s">
+      <c r="C101" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D101" s="9" t="s">
@@ -4331,19 +4327,19 @@
       <c r="E101" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F101" s="54" t="n">
+      <c r="F101" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G101" s="12"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C102" s="53" t="s">
+      <c r="C102" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D102" s="9" t="s">
@@ -4352,19 +4348,19 @@
       <c r="E102" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="F102" s="54" t="n">
+      <c r="F102" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G102" s="12"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12" t="s">
+      <c r="A103" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C103" s="53" t="s">
+      <c r="C103" s="52" t="s">
         <v>229</v>
       </c>
       <c r="D103" s="9" t="s">
@@ -4373,19 +4369,19 @@
       <c r="E103" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="F103" s="54" t="n">
+      <c r="F103" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G103" s="12"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12" t="s">
+      <c r="A104" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C104" s="47" t="s">
+      <c r="C104" s="46" t="s">
         <v>242</v>
       </c>
       <c r="D104" s="9" t="s">
@@ -4394,19 +4390,19 @@
       <c r="E104" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="F104" s="48" t="n">
+      <c r="F104" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="G104" s="12"/>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C105" s="47" t="s">
+      <c r="C105" s="46" t="s">
         <v>242</v>
       </c>
       <c r="D105" s="9" t="s">
@@ -4415,19 +4411,19 @@
       <c r="E105" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F105" s="48" t="n">
+      <c r="F105" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="12"/>
+      <c r="G105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C106" s="47" t="s">
+      <c r="C106" s="46" t="s">
         <v>242</v>
       </c>
       <c r="D106" s="9" t="s">
@@ -4436,19 +4432,19 @@
       <c r="E106" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="F106" s="48" t="n">
+      <c r="F106" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G106" s="12"/>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C107" s="47" t="s">
+      <c r="C107" s="46" t="s">
         <v>242</v>
       </c>
       <c r="D107" s="9" t="s">
@@ -4457,19 +4453,19 @@
       <c r="E107" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="F107" s="48" t="n">
+      <c r="F107" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="G107" s="12"/>
+      <c r="G107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C108" s="55" t="s">
+      <c r="C108" s="54" t="s">
         <v>251</v>
       </c>
       <c r="D108" s="9" t="s">
@@ -4478,19 +4474,19 @@
       <c r="E108" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F108" s="56" t="n">
+      <c r="F108" s="55" t="n">
         <v>6</v>
       </c>
-      <c r="G108" s="12"/>
+      <c r="G108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C109" s="55" t="s">
+      <c r="C109" s="54" t="s">
         <v>251</v>
       </c>
       <c r="D109" s="9" t="s">
@@ -4499,19 +4495,19 @@
       <c r="E109" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="F109" s="56" t="n">
+      <c r="F109" s="55" t="n">
         <v>6</v>
       </c>
-      <c r="G109" s="12"/>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C110" s="55" t="s">
+      <c r="C110" s="54" t="s">
         <v>251</v>
       </c>
       <c r="D110" s="9" t="s">
@@ -4520,19 +4516,19 @@
       <c r="E110" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="F110" s="56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" s="12"/>
+      <c r="F110" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" s="10"/>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="s">
+      <c r="A111" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C111" s="57" t="s">
+      <c r="C111" s="56" t="s">
         <v>258</v>
       </c>
       <c r="D111" s="9" t="s">
@@ -4541,19 +4537,19 @@
       <c r="E111" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="F111" s="58" t="n">
+      <c r="F111" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="G111" s="12"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C112" s="57" t="s">
+      <c r="C112" s="56" t="s">
         <v>258</v>
       </c>
       <c r="D112" s="9" t="s">
@@ -4562,19 +4558,19 @@
       <c r="E112" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="F112" s="58" t="n">
+      <c r="F112" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G112" s="12"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C113" s="57" t="s">
+      <c r="C113" s="56" t="s">
         <v>258</v>
       </c>
       <c r="D113" s="9" t="s">
@@ -4583,19 +4579,19 @@
       <c r="E113" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="F113" s="58" t="n">
+      <c r="F113" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="G113" s="12"/>
+      <c r="G113" s="10"/>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="58" t="s">
         <v>265</v>
       </c>
       <c r="D114" s="9" t="s">
@@ -4604,19 +4600,19 @@
       <c r="E114" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="F114" s="60" t="n">
+      <c r="F114" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="G114" s="12"/>
+      <c r="G114" s="10"/>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C115" s="59" t="s">
+      <c r="C115" s="58" t="s">
         <v>265</v>
       </c>
       <c r="D115" s="9" t="s">
@@ -4625,19 +4621,19 @@
       <c r="E115" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="F115" s="60" t="n">
+      <c r="F115" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="G115" s="12"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="12" t="s">
+      <c r="A116" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C116" s="59" t="s">
+      <c r="C116" s="58" t="s">
         <v>265</v>
       </c>
       <c r="D116" s="9" t="s">
@@ -4646,19 +4642,19 @@
       <c r="E116" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="F116" s="60" t="n">
+      <c r="F116" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G116" s="12"/>
+      <c r="G116" s="10"/>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="12" t="s">
+      <c r="A117" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C117" s="59" t="s">
+      <c r="C117" s="58" t="s">
         <v>265</v>
       </c>
       <c r="D117" s="9" t="s">
@@ -4667,19 +4663,19 @@
       <c r="E117" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="F117" s="60" t="n">
+      <c r="F117" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="G117" s="12"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="12" t="s">
+      <c r="A118" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C118" s="55" t="s">
+      <c r="C118" s="54" t="s">
         <v>274</v>
       </c>
       <c r="D118" s="9" t="s">
@@ -4688,19 +4684,19 @@
       <c r="E118" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F118" s="56" t="n">
+      <c r="F118" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G118" s="12"/>
+      <c r="G118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C119" s="55" t="s">
+      <c r="C119" s="54" t="s">
         <v>274</v>
       </c>
       <c r="D119" s="9" t="s">
@@ -4709,19 +4705,19 @@
       <c r="E119" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F119" s="56" t="n">
+      <c r="F119" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G119" s="12"/>
+      <c r="G119" s="10"/>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C120" s="55" t="s">
+      <c r="C120" s="54" t="s">
         <v>274</v>
       </c>
       <c r="D120" s="9" t="s">
@@ -4730,19 +4726,19 @@
       <c r="E120" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F120" s="56" t="n">
+      <c r="F120" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G120" s="12"/>
+      <c r="G120" s="10"/>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="12" t="s">
+      <c r="A121" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C121" s="55" t="s">
+      <c r="C121" s="54" t="s">
         <v>274</v>
       </c>
       <c r="D121" s="9" t="s">
@@ -4751,19 +4747,19 @@
       <c r="E121" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F121" s="56" t="n">
+      <c r="F121" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G121" s="12"/>
+      <c r="G121" s="10"/>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C122" s="55" t="s">
+      <c r="C122" s="54" t="s">
         <v>274</v>
       </c>
       <c r="D122" s="9" t="s">
@@ -4772,19 +4768,19 @@
       <c r="E122" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F122" s="56" t="n">
+      <c r="F122" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G122" s="12"/>
+      <c r="G122" s="10"/>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C123" s="61" t="s">
+      <c r="C123" s="60" t="s">
         <v>287</v>
       </c>
       <c r="D123" s="9" t="s">
@@ -4793,19 +4789,19 @@
       <c r="E123" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F123" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="G123" s="12"/>
+      <c r="F123" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G123" s="10"/>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C124" s="61" t="s">
+      <c r="C124" s="60" t="s">
         <v>287</v>
       </c>
       <c r="D124" s="9" t="s">
@@ -4814,19 +4810,19 @@
       <c r="E124" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F124" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="G124" s="12"/>
+      <c r="F124" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G124" s="10"/>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C125" s="61" t="s">
+      <c r="C125" s="60" t="s">
         <v>287</v>
       </c>
       <c r="D125" s="9" t="s">
@@ -4835,19 +4831,19 @@
       <c r="E125" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F125" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="G125" s="12"/>
+      <c r="F125" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G125" s="10"/>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C126" s="61" t="s">
+      <c r="C126" s="60" t="s">
         <v>287</v>
       </c>
       <c r="D126" s="9" t="s">
@@ -4856,19 +4852,19 @@
       <c r="E126" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="F126" s="62" t="n">
+      <c r="F126" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="G126" s="12"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12" t="s">
+      <c r="A127" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C127" s="61" t="s">
+      <c r="C127" s="60" t="s">
         <v>287</v>
       </c>
       <c r="D127" s="9" t="s">
@@ -4877,19 +4873,19 @@
       <c r="E127" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F127" s="62" t="n">
+      <c r="F127" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="G127" s="12"/>
+      <c r="G127" s="10"/>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C128" s="63" t="s">
+      <c r="C128" s="62" t="s">
         <v>298</v>
       </c>
       <c r="D128" s="9" t="s">
@@ -4898,19 +4894,19 @@
       <c r="E128" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="F128" s="64" t="n">
-        <v>8</v>
-      </c>
-      <c r="G128" s="12"/>
+      <c r="F128" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="12" t="s">
+      <c r="A129" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C129" s="63" t="s">
+      <c r="C129" s="62" t="s">
         <v>298</v>
       </c>
       <c r="D129" s="9" t="s">
@@ -4919,19 +4915,19 @@
       <c r="E129" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="F129" s="64" t="n">
+      <c r="F129" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="G129" s="12"/>
+      <c r="G129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C130" s="65" t="s">
+      <c r="C130" s="64" t="s">
         <v>303</v>
       </c>
       <c r="D130" s="9" t="s">
@@ -4940,19 +4936,19 @@
       <c r="E130" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F130" s="66" t="n">
+      <c r="F130" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="G130" s="12"/>
+      <c r="G130" s="10"/>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12" t="s">
+      <c r="A131" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="65" t="s">
+      <c r="C131" s="64" t="s">
         <v>303</v>
       </c>
       <c r="D131" s="9" t="s">
@@ -4961,19 +4957,19 @@
       <c r="E131" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="F131" s="66" t="n">
+      <c r="F131" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="G131" s="12"/>
+      <c r="G131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="12" t="s">
+      <c r="A132" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C132" s="65" t="s">
+      <c r="C132" s="64" t="s">
         <v>303</v>
       </c>
       <c r="D132" s="9" t="s">
@@ -4982,19 +4978,19 @@
       <c r="E132" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="F132" s="66" t="n">
+      <c r="F132" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="G132" s="12"/>
+      <c r="G132" s="10"/>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12" t="s">
+      <c r="A133" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B133" s="12" t="s">
+      <c r="B133" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C133" s="65" t="s">
+      <c r="C133" s="64" t="s">
         <v>303</v>
       </c>
       <c r="D133" s="9" t="s">
@@ -5003,19 +4999,19 @@
       <c r="E133" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="F133" s="66" t="n">
+      <c r="F133" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="G133" s="12"/>
+      <c r="G133" s="10"/>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C134" s="67" t="s">
+      <c r="C134" s="66" t="s">
         <v>312</v>
       </c>
       <c r="D134" s="9" t="s">
@@ -5024,19 +5020,19 @@
       <c r="E134" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="F134" s="68" t="n">
+      <c r="F134" s="67" t="n">
         <v>5</v>
       </c>
-      <c r="G134" s="12"/>
+      <c r="G134" s="10"/>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C135" s="67" t="s">
+      <c r="C135" s="66" t="s">
         <v>312</v>
       </c>
       <c r="D135" s="9" t="s">
@@ -5045,19 +5041,19 @@
       <c r="E135" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="F135" s="68" t="n">
+      <c r="F135" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="G135" s="12"/>
+      <c r="G135" s="10"/>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="12" t="s">
+      <c r="A136" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B136" s="12" t="s">
+      <c r="B136" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C136" s="67" t="s">
+      <c r="C136" s="66" t="s">
         <v>312</v>
       </c>
       <c r="D136" s="9" t="s">
@@ -5066,19 +5062,19 @@
       <c r="E136" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="F136" s="68" t="n">
+      <c r="F136" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="G136" s="12"/>
+      <c r="G136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="12" t="s">
+      <c r="A137" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B137" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C137" s="69" t="s">
+      <c r="C137" s="68" t="s">
         <v>319</v>
       </c>
       <c r="D137" s="9" t="s">
@@ -5087,19 +5083,19 @@
       <c r="E137" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="F137" s="70" t="n">
+      <c r="F137" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G137" s="12"/>
+      <c r="G137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="12" t="s">
+      <c r="A138" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="B138" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C138" s="69" t="s">
+      <c r="C138" s="68" t="s">
         <v>319</v>
       </c>
       <c r="D138" s="9" t="s">
@@ -5108,19 +5104,19 @@
       <c r="E138" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="F138" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="G138" s="12"/>
+      <c r="F138" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="G138" s="10"/>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="12" t="s">
+      <c r="A139" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C139" s="69" t="s">
+      <c r="C139" s="68" t="s">
         <v>319</v>
       </c>
       <c r="D139" s="9" t="s">
@@ -5129,19 +5125,19 @@
       <c r="E139" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="F139" s="70" t="n">
+      <c r="F139" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G139" s="12"/>
+      <c r="G139" s="10"/>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="12" t="s">
+      <c r="A140" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C140" s="69" t="s">
+      <c r="C140" s="68" t="s">
         <v>319</v>
       </c>
       <c r="D140" s="9" t="s">
@@ -5150,19 +5146,19 @@
       <c r="E140" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F140" s="70" t="n">
+      <c r="F140" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G140" s="12"/>
+      <c r="G140" s="10"/>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="12" t="s">
+      <c r="A141" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C141" s="71" t="s">
+      <c r="C141" s="70" t="s">
         <v>328</v>
       </c>
       <c r="D141" s="9" t="s">
@@ -5171,19 +5167,19 @@
       <c r="E141" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="F141" s="72" t="n">
+      <c r="F141" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G141" s="12"/>
+      <c r="G141" s="10"/>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="12" t="s">
+      <c r="A142" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C142" s="71" t="s">
+      <c r="C142" s="70" t="s">
         <v>328</v>
       </c>
       <c r="D142" s="9" t="s">
@@ -5192,19 +5188,19 @@
       <c r="E142" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="F142" s="72" t="n">
+      <c r="F142" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G142" s="12"/>
+      <c r="G142" s="10"/>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="12" t="s">
+      <c r="A143" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="71" t="s">
+      <c r="C143" s="70" t="s">
         <v>328</v>
       </c>
       <c r="D143" s="9" t="s">
@@ -5213,19 +5209,19 @@
       <c r="E143" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="F143" s="72" t="n">
+      <c r="F143" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G143" s="12"/>
+      <c r="G143" s="10"/>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="12" t="s">
+      <c r="A144" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B144" s="12" t="s">
+      <c r="B144" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="71" t="s">
+      <c r="C144" s="70" t="s">
         <v>328</v>
       </c>
       <c r="D144" s="9" t="s">
@@ -5234,19 +5230,19 @@
       <c r="E144" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="F144" s="72" t="n">
+      <c r="F144" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="G144" s="12"/>
+      <c r="G144" s="10"/>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="12" t="s">
+      <c r="A145" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C145" s="71" t="s">
+      <c r="C145" s="70" t="s">
         <v>328</v>
       </c>
       <c r="D145" s="9" t="s">
@@ -5255,10 +5251,10 @@
       <c r="E145" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="F145" s="72" t="n">
+      <c r="F145" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="G145" s="12"/>
+      <c r="G145" s="10"/>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6164,54 +6160,54 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="B2" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
+      <c r="B2" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="B3" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="72" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="72" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
